--- a/data/trans_orig/Q20A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q20A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que ha estado hospitalizado en los últimos 12 meses</t>
+          <t>Número medio de veces que la población ha estado hospitalizada en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,44 +716,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,07</t>
+          <t>0,02; 0,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,44</t>
+          <t>0,07; 0,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,04; 0,09</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,11</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,15</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 0,17</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,1</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0,05; 0,09</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,11</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,16</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,17</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,11</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,09</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>0,05; 0,1</t>
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,24</t>
+          <t>0,1; 0,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -856,57 +856,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,11</t>
+          <t>0,04; 0,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0,06; 0,11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,04; 0,16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 0,14</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,12</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,12</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,11</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>0,06; 0,1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,12</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,17</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,13</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,12</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,11</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,12</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,07</t>
+          <t>0,02; 0,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,07</t>
+          <t>0,04; 0,07</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,04; 0,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,21</t>
+          <t>0,07; 0,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,12</t>
+          <t>0,08; 0,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,14</t>
+          <t>0,07; 0,15</t>
         </is>
       </c>
     </row>
@@ -1281,27 +1281,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,13</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,08</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,12</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,13</t>
+          <t>0,1; 0,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">

--- a/data/trans_orig/Q20A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q20A-Habitat-trans_orig.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,35</t>
+          <t>0,07; 0,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,09</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,15</t>
+          <t>0,07; 0,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,17</t>
+          <t>0,1; 0,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,1</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,27</t>
+          <t>0,1; 0,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,09</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,04; 0,11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0,04; 0,12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,26</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 0,14</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,12</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,11</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>0,06; 0,11</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,13</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,16</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,13</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,12</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,11</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,1</t>
-        </is>
-      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,13</t>
+          <t>0,07; 0,15</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,09</t>
+          <t>0,04; 0,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,19</t>
+          <t>0,09; 0,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,07; 0,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,07</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,13</t>
+          <t>0,08; 0,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,07</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,22</t>
+          <t>0,07; 0,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,16</t>
+          <t>0,09; 0,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,1</t>
+          <t>0,07; 0,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,13</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,15</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
     </row>
@@ -1223,27 +1223,27 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0,08</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,05; 0,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,07; 0,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,12</t>
+          <t>0,09; 0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,08</t>
+          <t>0,07; 0,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,09</t>
+          <t>0,07; 0,1</t>
         </is>
       </c>
     </row>
